--- a/db/tablas_procesadas/Dia_operativo_curso.xlsx
+++ b/db/tablas_procesadas/Dia_operativo_curso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1647637-D61A-4DC4-905B-29626E5B4D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37ED5389-DA28-410C-AC12-9ECE59CB0769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="4800" windowWidth="28785" windowHeight="15345" xr2:uid="{43BD1C35-1044-4333-8111-FC055DAB3252}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{43BD1C35-1044-4333-8111-FC055DAB3252}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -179,9 +179,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -219,7 +219,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -325,7 +325,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -467,7 +467,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -476,13 +476,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227DFF5F-21B1-4BD3-92F2-CAA5E8FFE88C}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -502,7 +502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -522,7 +522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -542,7 +542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -562,7 +562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -582,7 +582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -602,7 +602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -622,7 +622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -642,7 +642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -662,7 +662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -682,7 +682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -702,7 +702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -722,7 +722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -742,7 +742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -782,7 +782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -802,7 +802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -822,7 +822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -842,7 +842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -862,7 +862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -882,7 +882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -902,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -922,7 +922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
